--- a/data-source/ESTOQUEEADI.xlsx
+++ b/data-source/ESTOQUEEADI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smart group - 1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/Relatórios SMART-STOCK/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9897BC62-682C-4517-9EDE-CEAFBFF248A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9897BC62-682C-4517-9EDE-CEAFBFF248A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06E5C60B-4950-4087-8802-EE23AFCAE01C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4B53B3B2-3DBF-46E3-8DE0-D597078CC745}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4B53B3B2-3DBF-46E3-8DE0-D597078CC745}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Produto</t>
   </si>
@@ -107,9 +107,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -147,7 +147,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -253,7 +253,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -395,7 +395,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -403,17 +403,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B43164-A157-422F-BA0D-8470CD7BA9D2}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -430,7 +430,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>9295</v>
       </c>
@@ -447,7 +447,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>16904</v>
       </c>
@@ -461,23 +461,6 @@
         <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>16904</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>14306</v>
-      </c>
-      <c r="D4">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data-source/ESTOQUEEADI.xlsx
+++ b/data-source/ESTOQUEEADI.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/Relatórios SMART-STOCK/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9897BC62-682C-4517-9EDE-CEAFBFF248A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06E5C60B-4950-4087-8802-EE23AFCAE01C}"/>
